--- a/middleware/sample.xlsx
+++ b/middleware/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melfa_middleware\middleware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B982EB86-6B19-42D9-8934-B388CCC4C8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D0A518-E383-4AB4-B4BA-3C3E82CC6337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="48">
   <si>
     <t>command</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>1;1;OVRD=</t>
+  </si>
+  <si>
+    <t>testsv</t>
+  </si>
+  <si>
+    <t>1;1;ERRORRD&lt;;0</t>
   </si>
 </sst>
 </file>
@@ -480,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -951,6 +957,14 @@
         <v>44</v>
       </c>
     </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>47</v>
+      </c>
+      <c r="B59" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/middleware/sample.xlsx
+++ b/middleware/sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melfa_middleware\middleware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D0A518-E383-4AB4-B4BA-3C3E82CC6337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E77B8E-A247-4EB9-9915-A3A4F898ED14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2496" yWindow="888" windowWidth="17220" windowHeight="8844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="52">
   <si>
     <t>command</t>
   </si>
@@ -169,19 +169,36 @@
   </si>
   <si>
     <t>1;1;ERRORRD&lt;;0</t>
+  </si>
+  <si>
+    <t>prgrm</t>
+  </si>
+  <si>
+    <t>testprgrm:=</t>
+  </si>
+  <si>
+    <t>1;-1;PPOSF</t>
+  </si>
+  <si>
+    <t>pposf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -204,8 +221,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -965,7 +985,24 @@
         <v>46</v>
       </c>
     </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>49</v>
+      </c>
+      <c r="B60" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/middleware/sample.xlsx
+++ b/middleware/sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melfa_middleware\middleware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E77B8E-A247-4EB9-9915-A3A4F898ED14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA18D6C-2007-4D42-88EE-462DF2368E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2496" yWindow="888" windowWidth="17220" windowHeight="8844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="101">
   <si>
     <t>command</t>
   </si>
@@ -181,6 +181,153 @@
   </si>
   <si>
     <t>pposf</t>
+  </si>
+  <si>
+    <t>1;1;RSTALRM</t>
+  </si>
+  <si>
+    <t>rstalarm</t>
+  </si>
+  <si>
+    <t>1;0;JOGST</t>
+  </si>
+  <si>
+    <t>1;1;OUT=900;2</t>
+  </si>
+  <si>
+    <t>1;1;OUT=900;1</t>
+  </si>
+  <si>
+    <t>opengripper</t>
+  </si>
+  <si>
+    <t>closegripper</t>
+  </si>
+  <si>
+    <t>emgstop</t>
+  </si>
+  <si>
+    <t>1;1;BZR</t>
+  </si>
+  <si>
+    <t>buzzer</t>
+  </si>
+  <si>
+    <t>j1mm</t>
+  </si>
+  <si>
+    <t>1;1;JSAFE</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;0;1;0</t>
+  </si>
+  <si>
+    <t>xplus</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;1;0;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;1;0;0</t>
+  </si>
+  <si>
+    <t>xminus</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;0;1;0</t>
+  </si>
+  <si>
+    <t>yplus</t>
+  </si>
+  <si>
+    <t>yminus</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;0;2;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;0;2;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;2;0;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;2;0;0</t>
+  </si>
+  <si>
+    <t>zplus</t>
+  </si>
+  <si>
+    <t>zminus</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;0;4;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;0;4;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;4;0;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;4;0;0</t>
+  </si>
+  <si>
+    <t>aplus</t>
+  </si>
+  <si>
+    <t>aminus</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;0;8;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;0;8;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;8;0;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;8;0;0</t>
+  </si>
+  <si>
+    <t>bplus</t>
+  </si>
+  <si>
+    <t>bminus</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;0;10;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;0;10;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;10;0;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;10;0;0</t>
+  </si>
+  <si>
+    <t>cplus</t>
+  </si>
+  <si>
+    <t>cminus</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;0;20;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;0;20;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG01;64;20;0;0</t>
+  </si>
+  <si>
+    <t>1;1;JOG11;64;20;0;0</t>
   </si>
 </sst>
 </file>
@@ -506,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -1001,6 +1148,470 @@
         <v>51</v>
       </c>
     </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>54</v>
+      </c>
+      <c r="B63" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>60</v>
+      </c>
+      <c r="B66" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B68" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>73</v>
+      </c>
+      <c r="B81" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B82" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>75</v>
+      </c>
+      <c r="B85" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>76</v>
+      </c>
+      <c r="B86" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>80</v>
+      </c>
+      <c r="B90" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>81</v>
+      </c>
+      <c r="B93" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>82</v>
+      </c>
+      <c r="B94" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>86</v>
+      </c>
+      <c r="B98" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>87</v>
+      </c>
+      <c r="B101" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>88</v>
+      </c>
+      <c r="B102" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B103" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>91</v>
+      </c>
+      <c r="B105" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>92</v>
+      </c>
+      <c r="B106" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>93</v>
+      </c>
+      <c r="B109" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>94</v>
+      </c>
+      <c r="B110" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>7</v>
+      </c>
+      <c r="B111" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>97</v>
+      </c>
+      <c r="B113" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>98</v>
+      </c>
+      <c r="B114" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>99</v>
+      </c>
+      <c r="B117" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>100</v>
+      </c>
+      <c r="B118" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/middleware/sample.xlsx
+++ b/middleware/sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melfa_middleware\middleware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA18D6C-2007-4D42-88EE-462DF2368E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8BB323-77BC-4F56-85FA-716BDAD33B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="103">
   <si>
     <t>command</t>
   </si>
@@ -328,6 +328,12 @@
   </si>
   <si>
     <t>1;1;JOG11;64;20;0;0</t>
+  </si>
+  <si>
+    <t>1;-1;JPOSF</t>
+  </si>
+  <si>
+    <t>posf</t>
   </si>
 </sst>
 </file>
@@ -653,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -1612,6 +1618,14 @@
         <v>96</v>
       </c>
     </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>101</v>
+      </c>
+      <c r="B120" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/middleware/sample.xlsx
+++ b/middleware/sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melfa_middleware\middleware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8BB323-77BC-4F56-85FA-716BDAD33B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FE594C-BA22-4027-9880-BF1B65D57360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="103">
   <si>
     <t>command</t>
   </si>
@@ -659,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -1172,39 +1172,39 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B68" t="s">
         <v>62</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
         <v>62</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B70" t="s">
         <v>62</v>
@@ -1228,23 +1228,23 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B73" t="s">
         <v>66</v>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
         <v>66</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="B75" t="s">
         <v>66</v>
@@ -1268,15 +1268,15 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="B77" t="s">
         <v>69</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s">
         <v>69</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
         <v>69</v>
@@ -1300,15 +1300,15 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="B81" t="s">
         <v>71</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B82" t="s">
         <v>71</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B83" t="s">
         <v>71</v>
@@ -1332,15 +1332,15 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B85" t="s">
         <v>72</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B86" t="s">
         <v>72</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s">
         <v>72</v>
@@ -1364,15 +1364,15 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="B89" t="s">
         <v>77</v>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B90" t="s">
         <v>77</v>
@@ -1388,7 +1388,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="B91" t="s">
         <v>77</v>
@@ -1396,15 +1396,15 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="B93" t="s">
         <v>78</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B94" t="s">
         <v>78</v>
@@ -1420,7 +1420,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B95" t="s">
         <v>78</v>
@@ -1428,15 +1428,15 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="B97" t="s">
         <v>83</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B98" t="s">
         <v>83</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="B99" t="s">
         <v>83</v>
@@ -1460,15 +1460,15 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="B101" t="s">
         <v>84</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B102" t="s">
         <v>84</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="B103" t="s">
         <v>84</v>
@@ -1492,15 +1492,15 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="B105" t="s">
         <v>89</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B106" t="s">
         <v>89</v>
@@ -1516,7 +1516,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="B107" t="s">
         <v>89</v>
@@ -1524,15 +1524,15 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="B109" t="s">
         <v>90</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B110" t="s">
         <v>90</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="B111" t="s">
         <v>90</v>
@@ -1556,15 +1556,15 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="B113" t="s">
         <v>95</v>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B114" t="s">
         <v>95</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="B115" t="s">
         <v>95</v>
@@ -1588,15 +1588,15 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="B117" t="s">
         <v>96</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B118" t="s">
         <v>96</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="B119" t="s">
         <v>96</v>
@@ -1620,9 +1620,17 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>7</v>
+      </c>
+      <c r="B120" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>101</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" t="s">
         <v>102</v>
       </c>
     </row>

--- a/middleware/sample.xlsx
+++ b/middleware/sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\melfa_middleware\middleware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FE594C-BA22-4027-9880-BF1B65D57360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A87672-872F-4785-A0CC-05BC984A44D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12900" yWindow="8184" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="131">
   <si>
     <t>command</t>
   </si>
@@ -334,6 +334,90 @@
   </si>
   <si>
     <t>posf</t>
+  </si>
+  <si>
+    <t>1;1;FDELTESTT</t>
+  </si>
+  <si>
+    <t>del</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>1;1;RUNSHOWOF;1</t>
+  </si>
+  <si>
+    <t>1;1;PDIR&lt;</t>
+  </si>
+  <si>
+    <t>prnum</t>
+  </si>
+  <si>
+    <t>1;1;PDIR01</t>
+  </si>
+  <si>
+    <t>1;1;PDIR02</t>
+  </si>
+  <si>
+    <t>1;1;PDIR03</t>
+  </si>
+  <si>
+    <t>1;1;PDIR04</t>
+  </si>
+  <si>
+    <t>1;1;PDIR05</t>
+  </si>
+  <si>
+    <t>1;1;PDIR06</t>
+  </si>
+  <si>
+    <t>1;1;PDIR07</t>
+  </si>
+  <si>
+    <t>1;1;PDIR08</t>
+  </si>
+  <si>
+    <t>1;1;PDIR09</t>
+  </si>
+  <si>
+    <t>1;1;PDIR10</t>
+  </si>
+  <si>
+    <t>pr1</t>
+  </si>
+  <si>
+    <t>pr2</t>
+  </si>
+  <si>
+    <t>pr3</t>
+  </si>
+  <si>
+    <t>pr4</t>
+  </si>
+  <si>
+    <t>pr5</t>
+  </si>
+  <si>
+    <t>pr6</t>
+  </si>
+  <si>
+    <t>pr7</t>
+  </si>
+  <si>
+    <t>pr8</t>
+  </si>
+  <si>
+    <t>pr9</t>
+  </si>
+  <si>
+    <t>pr10</t>
+  </si>
+  <si>
+    <t>RunPrgm</t>
+  </si>
+  <si>
+    <t>runP</t>
   </si>
 </sst>
 </file>
@@ -659,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:B137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -1634,6 +1718,134 @@
         <v>102</v>
       </c>
     </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>103</v>
+      </c>
+      <c r="B122" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>106</v>
+      </c>
+      <c r="B124" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>7</v>
+      </c>
+      <c r="B125" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>107</v>
+      </c>
+      <c r="B126" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>109</v>
+      </c>
+      <c r="B127" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>110</v>
+      </c>
+      <c r="B128" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>111</v>
+      </c>
+      <c r="B129" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>112</v>
+      </c>
+      <c r="B130" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>113</v>
+      </c>
+      <c r="B131" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>114</v>
+      </c>
+      <c r="B132" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>115</v>
+      </c>
+      <c r="B133" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>116</v>
+      </c>
+      <c r="B134" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>117</v>
+      </c>
+      <c r="B135" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>118</v>
+      </c>
+      <c r="B136" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>130</v>
+      </c>
+      <c r="B137" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
